--- a/www/ig/fhir/mesures/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$94</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3290" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/vitalsigns</t>
+    <t>http://hl7.org/fhir/StructureDefinition/headcircum</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -272,10 +272,10 @@
 </t>
   </si>
   <si>
-    <t>FHIR Vital Signs Profile</t>
-  </si>
-  <si>
-    <t>The FHIR Vitals Signs profile sets minimum expectations for the Observation Resource to record, search and fetch the vital signs associated with a patient.</t>
+    <t>FHIR Head Circumference Profile</t>
+  </si>
+  <si>
+    <t>This profile defines  how to represent Head Circumference observations in FHIR using a standard LOINC code and UCUM units of measure.</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -439,8 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -456,7 +455,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -494,7 +493,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +517,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -644,7 +643,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -660,7 +659,8 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -718,7 +718,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -747,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -827,7 +827,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1063,17 +1063,17 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Coded Responses from C-CDA Vital Sign Results</t>
-  </si>
-  <si>
-    <t>Coded Responses from C-CDA Vital Sign Results.</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+    <t>Name
+Test</t>
+  </si>
+  <si>
+    <t>Head Circumference</t>
+  </si>
+  <si>
+    <t>Head Circumference.</t>
+  </si>
+  <si>
+    <t>additional codes that translate or map to this code are allowed.  For example a more granular LOINC code or code that is used locally in a system.</t>
   </si>
   <si>
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
@@ -1082,7 +1082,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1110,10 +1110,67 @@
   </si>
   <si>
     <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>value:code}
 value:system}</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode</t>
+  </si>
+  <si>
+    <t>HeadCircumCode</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>9843-4</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:HeadCircumCode.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding:headCircumCode</t>
@@ -1165,7 +1222,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1283,7 +1340,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1328,6 +1385,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>obs-7
 vs-2</t>
   </si>
@@ -1344,10 +1404,25 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
     <t>Observation.value[x].id</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
     <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value</t>
   </si>
   <si>
     <t>Observation.value[x].value</t>
@@ -1378,6 +1453,9 @@
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
     <t>Observation.value[x].comparator</t>
   </si>
   <si>
@@ -1408,6 +1486,9 @@
     <t>IVL properties</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
     <t>Observation.value[x].unit</t>
   </si>
   <si>
@@ -1430,6 +1511,9 @@
   </si>
   <si>
     <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
   </si>
   <si>
     <t>Observation.value[x].system</t>
@@ -1457,19 +1541,25 @@
     <t>CO.codeSystem, PQ.translation.codeSystem</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
     <t>Observation.value[x].code</t>
   </si>
   <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
+    <t>Coded responses from the common UCUM units for vital signs value set.</t>
   </si>
   <si>
     <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Common UCUM units for body length measures such as Body Height and Head Circumference.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/ucum-bodylength|4.0.1</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -1497,7 +1587,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1529,7 +1619,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1585,7 +1675,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1618,7 +1708,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1630,7 +1720,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1739,7 +1829,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1789,7 +1879,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1822,7 +1912,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1859,7 +1949,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1881,7 +1971,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2319,20 +2409,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2341,28 +2431,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5127,7 +5217,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -5367,7 +5457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>263</v>
       </c>
@@ -5729,7 +5819,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>269</v>
       </c>
@@ -6089,7 +6179,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>282</v>
       </c>
@@ -6331,7 +6421,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>300</v>
       </c>
@@ -6815,7 +6905,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>336</v>
       </c>
@@ -7188,7 +7278,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -7252,7 +7342,7 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7297,13 +7387,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
@@ -7347,7 +7437,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7424,7 +7514,7 @@
         <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7444,23 +7534,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>108</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7508,7 +7594,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7520,7 +7606,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7529,10 +7615,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7543,46 +7629,44 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>115</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>116</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7618,46 +7702,46 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7665,10 +7749,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7676,10 +7760,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7691,24 +7775,26 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7750,13 +7836,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7771,13 +7857,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7785,14 +7871,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7811,20 +7897,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7872,7 +7956,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7887,19 +7971,19 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>383</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7907,14 +7991,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7924,7 +8008,7 @@
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7933,26 +8017,24 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>391</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -7994,7 +8076,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8003,25 +8085,25 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>395</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8029,10 +8111,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8055,18 +8137,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>399</v>
+        <v>311</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8114,7 +8196,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>398</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8135,13 +8217,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8149,10 +8231,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8163,7 +8245,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8175,17 +8257,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>407</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>409</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8234,13 +8318,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8249,19 +8333,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>411</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>412</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8269,24 +8353,26 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8295,19 +8381,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>415</v>
+        <v>147</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>272</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>273</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>274</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8317,7 +8403,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8344,26 +8430,28 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>275</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8372,27 +8460,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>276</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>277</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8412,19 +8500,23 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8472,7 +8564,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>110</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8484,7 +8576,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8493,10 +8585,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>111</v>
+        <v>335</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8505,46 +8597,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>115</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>116</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8580,46 +8674,46 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>121</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>111</v>
+        <v>385</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8627,10 +8721,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8638,10 +8732,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8653,20 +8747,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8714,13 +8806,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8735,13 +8827,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>346</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8749,14 +8841,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8769,30 +8861,30 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>395</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>439</v>
+        <v>399</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q54" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8812,13 +8904,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8836,7 +8928,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8851,44 +8943,44 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -8897,17 +8989,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>449</v>
+        <v>410</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8917,7 +9011,7 @@
         <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>82</v>
@@ -8956,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8965,25 +9059,25 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>412</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8991,10 +9085,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9017,18 +9111,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9037,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9076,7 +9170,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9085,7 +9179,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9097,13 +9191,13 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9111,10 +9205,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9122,10 +9216,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9137,19 +9231,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>425</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>466</v>
+        <v>428</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9198,13 +9290,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>467</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9213,19 +9305,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9233,10 +9325,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9256,22 +9348,22 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>434</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9296,31 +9388,29 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9329,7 +9419,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9338,62 +9428,64 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>192</v>
+        <v>442</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D59" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>434</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9418,13 +9510,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9442,16 +9534,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9460,27 +9552,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>442</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>489</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9491,7 +9583,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9503,20 +9595,16 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>491</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9564,19 +9652,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9585,10 +9673,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>497</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9599,21 +9687,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9625,16 +9713,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>499</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>500</v>
+        <v>116</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>501</v>
+        <v>117</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9660,69 +9748,69 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>506</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9730,34 +9818,34 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>511</v>
+        <v>456</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>512</v>
+        <v>457</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9782,13 +9870,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9806,7 +9894,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>458</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9827,10 +9915,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9841,10 +9929,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9861,28 +9949,30 @@
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>518</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>519</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9902,13 +9992,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9926,7 +10016,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9944,27 +10034,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>523</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>526</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>526</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9972,7 +10062,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -9984,21 +10074,21 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>527</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>528</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10007,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>82</v>
@@ -10046,7 +10136,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10064,27 +10154,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>532</v>
+        <v>479</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>533</v>
+        <v>480</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>535</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10092,41 +10182,39 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>536</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>537</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>540</v>
+        <v>485</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10168,19 +10256,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>535</v>
+        <v>487</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>541</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10189,10 +10277,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>542</v>
+        <v>479</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>543</v>
+        <v>489</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10201,12 +10289,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>544</v>
+        <v>490</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10214,31 +10302,35 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>108</v>
+        <v>492</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10247,7 +10339,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10262,13 +10354,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10286,7 +10378,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>110</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10298,7 +10390,7 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10307,10 +10399,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>111</v>
+        <v>498</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10319,26 +10411,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10347,18 +10439,20 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>115</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>116</v>
+        <v>501</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10382,13 +10476,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10406,19 +10500,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>121</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10427,10 +10521,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>111</v>
+        <v>507</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10441,14 +10535,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10461,25 +10555,25 @@
         <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>548</v>
+        <v>510</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>117</v>
+        <v>512</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>211</v>
+        <v>513</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10504,13 +10598,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10528,7 +10622,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>550</v>
+        <v>508</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10540,33 +10634,33 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>192</v>
+        <v>518</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10577,7 +10671,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10589,16 +10683,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>552</v>
+        <v>521</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>553</v>
+        <v>522</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10646,16 +10744,16 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10667,10 +10765,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10681,10 +10779,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10707,15 +10805,17 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>552</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10740,13 +10840,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10764,7 +10864,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10773,7 +10873,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10782,27 +10882,27 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>561</v>
+        <v>536</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10828,16 +10928,16 @@
         <v>253</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10862,13 +10962,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>567</v>
+        <v>543</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10886,7 +10986,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10904,13 +11004,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10921,10 +11021,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10935,7 +11035,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10947,20 +11047,18 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>253</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>572</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10984,13 +11082,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11008,13 +11106,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11026,27 +11124,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>488</v>
+        <v>554</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11060,7 +11158,7 @@
         <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11069,18 +11167,18 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11128,7 +11226,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11146,27 +11244,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11177,7 +11275,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11189,16 +11287,20 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>566</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11246,19 +11348,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>571</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11267,10 +11369,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11281,10 +11383,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11295,7 +11397,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11304,20 +11406,18 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>589</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>590</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11366,19 +11466,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>588</v>
+        <v>110</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11387,10 +11487,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>594</v>
+        <v>111</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11401,14 +11501,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11424,19 +11524,19 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>596</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>597</v>
+        <v>115</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>598</v>
+        <v>116</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>599</v>
+        <v>117</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11486,7 +11586,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>595</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11498,7 +11598,7 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11507,10 +11607,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>600</v>
+        <v>111</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11521,14 +11621,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11538,28 +11638,28 @@
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>536</v>
+        <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>603</v>
+        <v>117</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>604</v>
+        <v>211</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11608,7 +11708,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11620,7 +11720,7 @@
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>605</v>
+        <v>122</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11629,10 +11729,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>607</v>
+        <v>192</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11643,10 +11743,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11669,13 +11769,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>582</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
+        <v>584</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11726,7 +11826,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11735,10 +11835,10 @@
         <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11747,10 +11847,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>111</v>
+        <v>587</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11761,21 +11861,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11787,17 +11887,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>114</v>
+        <v>582</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11846,19 +11944,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11867,10 +11965,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>111</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11881,45 +11979,45 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>549</v>
+        <v>594</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>117</v>
+        <v>595</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>211</v>
+        <v>596</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11944,13 +12042,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11968,31 +12066,31 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>550</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>192</v>
+        <v>518</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12003,10 +12101,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12014,34 +12112,34 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>253</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12066,13 +12164,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>342</v>
+        <v>606</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>343</v>
+        <v>607</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12090,13 +12188,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12108,16 +12206,16 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>346</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>347</v>
+        <v>518</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
@@ -12125,10 +12223,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12142,28 +12240,26 @@
         <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>418</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12188,13 +12284,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12212,7 +12308,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12221,7 +12317,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12230,27 +12326,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>423</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12264,7 +12360,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12273,20 +12369,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12310,13 +12402,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12334,7 +12426,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12343,7 +12435,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12355,10 +12447,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>192</v>
+        <v>586</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12369,14 +12461,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12392,23 +12484,21 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12432,13 +12522,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12456,7 +12546,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12474,27 +12564,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>487</v>
+        <v>623</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>488</v>
+        <v>624</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12514,23 +12604,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>83</v>
+        <v>626</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12578,7 +12666,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12599,30 +12687,1122 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>542</v>
+        <v>623</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>543</v>
+        <v>630</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP94">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
